--- a/ig/ch-term/ValueSet-ch-vacd-vaccines-snomedct-vs.xlsx
+++ b/ig/ch-term/ValueSet-ch-vacd-vaccines-snomedct-vs.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="479" uniqueCount="476">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="483" uniqueCount="480">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>3.3.0</t>
+    <t>3.4.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-15T10:47:47+00:00</t>
+    <t>2026-06-10T10:00:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1432,6 +1432,18 @@
   </si>
   <si>
     <t>Live attenuated Mycobacterium bovis antigen only vaccine product in parenteral dose form</t>
+  </si>
+  <si>
+    <t>1345202008</t>
+  </si>
+  <si>
+    <t>Chikungunya virus antigen-containing vaccine product</t>
+  </si>
+  <si>
+    <t>1344967001</t>
+  </si>
+  <si>
+    <t>Live attenuated Chikungunya virus antigen</t>
   </si>
   <si>
     <t/>
@@ -1714,7 +1726,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B224"/>
+  <dimension ref="A1:B226"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -3502,15 +3514,31 @@
         <v>473</v>
       </c>
       <c r="B223" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B224" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="s" s="2">
+        <v>477</v>
+      </c>
+      <c r="B225" t="s" s="2">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="s" s="2">
+        <v>478</v>
+      </c>
+      <c r="B226" t="s" s="2">
+        <v>479</v>
       </c>
     </row>
   </sheetData>
